--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -600,12 +600,12 @@
     <row r="6" ht="100" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>① 対照は39件である</t>
+          <t>① 対照は38件である</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>中間報告の第1節から第6節までに記載した主要な数値・主張を39件抽出し、それぞれについて「出典」「本集のどのファイル・どのシートで確認できるか」「どのように検算できるか」を示した（01シート）。中間報告に現れる数値表現は延べ107・ユニーク91であり、本集はそのうち評価の判断に関わるものを抽出している。</t>
+          <t>中間報告の第1節から第6節までに記載した主要な数値・主張を38件抽出し、それぞれについて「出典」「本集のどのファイル・どのシートで確認できるか」「どのように検算できるか」を示した（01シート）。中間報告に現れる数値表現は延べ107・ユニーク91であり、本集はそのうち評価の判断に関わるものを抽出している。</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>01シートの「確からしさ」欄で、出典から直接確認できるもの（確定）と、受託者の判断が入るもの・留保があるものを分けている。出典から直接確認できるもの（「確定」）30件、受託者の判断や出典側の留保を伴うもの9件である。</t>
+          <t>01シートの「確からしさ」欄で、出典から直接確認できるもの（確定）と、受託者の判断が入るもの・留保があるものを分けている。出典から直接確認できるもの（「確定」）29件、受託者の判断や出典側の留保を伴うもの9件である。</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>中間報告の記述と根拠の対照（39件）</t>
+          <t>中間報告の記述と根拠の対照（38件）</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>★令和3年度以降は見える化にデータ登録がなく令和2年度が最新</t>
+          <t>令和3年度以降は見える化にデータ登録がなく令和2年度が最新</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>★δには「自治体向けのため取り扱いに注意」の記載がある</t>
+          <t>δには「自治体向けのため取り扱いに注意」の記載がある</t>
         </is>
       </c>
     </row>
@@ -2107,32 +2107,32 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>レッドチームレビューの指摘</t>
+          <t>評価方法の妥当性確認で扱った論点</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>29件（重大11・中14・軽微4）</t>
+          <t>6件</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>受託者による自己点検</t>
+          <t>受託者による内部点検</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>第9期評価のレッドチームレビュー 01_指摘一覧</t>
+          <t>本表01シート及び中間報告 第6節</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>同シートの件数を区分別に数える</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>確定</t>
+          <t>中間報告 第6節の表に掲げた論点を数える</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>確定（論点の抽出は受託者の判断）</t>
         </is>
       </c>
     </row>
@@ -2144,83 +2144,46 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>修正した誤読3点</t>
+          <t>受給率×受給者単価は給付月額指数に一致しない</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>3点</t>
+          <t>上川管内21保険者のうち16保険者で0.03を超える差</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>見える化D49・地域差指数</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>第9期評価のレッドチームレビュー 07_対応方針・08_対応の実施結果</t>
+          <t>地域差の分析／妥当性検証報告書 13_受給率の内訳と推移</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>対応済みの指摘のうち主要なものを抽出したもの</t>
-        </is>
-      </c>
-      <c r="G42" s="9" t="inlineStr">
-        <is>
-          <t>確定（抽出は受託者の判断）</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="40" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>第6節</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>受給率×受給者単価は給付月額指数に一致しない</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>上川管内21保険者のうち16保険者で0.03を超える差</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>見える化D49・地域差指数</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>地域差の分析／妥当性検証報告書 13_受給率の内訳と推移</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
           <t>21保険者について受給率×単価と給付月額指数の差を算定する</t>
         </is>
       </c>
-      <c r="G43" s="8" t="inlineStr">
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>確定</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>注1）節別の件数は第1節 1件、第3節1 10件、第3節2 12件、第4節 10件、第5節 3件、第6節 3件である。注2）「確からしさ」が「確定」でないものは、受託者の判断による抽出・判定が入るか、出典側に留保があるものである。注3）★を付した項目は、とくに留意を要する。</t>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>注1）節別の件数は第1節 1件、第3節1 10件、第3節2 12件、第4節 10件、第5節 3件、第6節 2件である。注2）「確からしさ」が「確定」でないものは、受託者の判断による抽出・判定が入るか、出典側に留保があるものである。注3）を付した項目は、とくに留意を要する。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A43:G43"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A44:G44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2691,7 +2654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2761,7 +2724,7 @@
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -2770,7 +2733,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>af4b205050f153f66de88af352eaa57e2749c95aaf0a21a222c5e10ece97bfb3</t>
+          <t>4b06eecdd9e32b179844e3b2745585d7045c503987d4b28500140e4fd78f7929</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -2828,7 +2791,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>b8c0e214c1211d9eb2994e7a8af27bfb5c6db0de1a1b57a8269d6e110838b96b</t>
+          <t>8cf4888348dd22055c7fb41a5204a146cdfb6b971c4d4e959007d83176bf5721</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -2845,23 +2808,23 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
+          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>8e57ed0b57632c1479fd4d05d5501967b4b9166f043fabc7b213439d02f720e8</t>
+          <t>0a93a013b0a4afae4999a69d216821d25f28cb822f5abdb32df80d6630760cd8</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>9シート。評価への指摘29件と対応</t>
+          <t>7シート。19施策と4調査・代表KPIの対応</t>
         </is>
       </c>
     </row>
@@ -2873,23 +2836,23 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
+          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>cebd894b4cd6e4667d30e2b1184bfe7e07c472819ec4424af1b5eb5088dc136c</t>
+          <t>e997c65a7218dc508cddda3773e36185a1d385f0efc4b26c1e5f8a4d67e55c4c</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>7シート。19施策と4調査・代表KPIの対応</t>
+          <t>6シート。評価表の受け皿・入力様式・暫定ルール・スコアカード</t>
         </is>
       </c>
     </row>
@@ -2901,23 +2864,23 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>81f452cee536110aeef7caeef5e14b51c032160056d99688fba6df10d0c365ec</t>
+          <t>aeeac320205f4e97239b1d7cc74b0fd7e22565f4b33d020459bb8ac9dfe0ffc4</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>6シート。評価表の受け皿・入力様式・暫定ルール・スコアカード</t>
+          <t>8シート。主張ごとの根拠水準、不足資料18件</t>
         </is>
       </c>
     </row>
@@ -2929,23 +2892,23 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>9b4af702cb6365fa2600b3c24dd64274a43abec682878c185680b9ec36fda28b</t>
+          <t>184414df7bc556d2c4c815e6d9154ef9c390545a7f551c7804fb77c5fb439d06</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>8シート。主張ごとの根拠水準、不足資料18件</t>
+          <t>5シート。第9期と第10期の基本目標・施策・KPIの対照</t>
         </is>
       </c>
     </row>
@@ -2957,23 +2920,23 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>a942d9afb64260ad4c0a9bcb8eea443a34efa8bc89ac27ac6e40e12288833d39</t>
+          <t>1c31def6332847387f7c2908ed866e58195a0e12e1aed56ba964734ab6314741</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>5シート。第9期と第10期の基本目標・施策・KPIの対照</t>
+          <t>認定率の年齢階級別・年齢調整の分析</t>
         </is>
       </c>
     </row>
@@ -2985,23 +2948,23 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>32c96504c0ff2861010475375ab0c194bd044c8a6cd8cb101b09ea8f42c6dc6f</t>
+          <t>0d7b86ae9ff047a7db7df12dbaf2b44b9819f9522e3ba3e0e379f5a23c1d6b3d</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>認定率の年齢階級別・年齢調整の分析</t>
+          <t>自給率・給付水準の地域差の分析</t>
         </is>
       </c>
     </row>
@@ -3013,23 +2976,23 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>5b314289bf4b52ac58e25d4cac7eea60c7eee2ecf7452ae6a610f966395c5237</t>
+          <t>c407617d337c4dedfda93a26e65ec717d54647c58212f82e5806bf4450e0ef26</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差の分析</t>
+          <t>24シート。健康とくらしの調査の個票によるクロス集計</t>
         </is>
       </c>
     </row>
@@ -3041,23 +3004,23 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>d307a84f4c8ca4590ae6d3e65a3cf4ff340c1140890c22e07e110ec98bd42698</t>
+          <t>71485c441972aac9fe3afbf49b929c86e458de6b40b57c98a868102502101777</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>24シート。健康とくらしの調査の個票によるクロス集計</t>
+          <t>15シート。4調査の集計と限界・留保</t>
         </is>
       </c>
     </row>
@@ -3069,23 +3032,23 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>bffdc2d6c9bc74af4687138ad57269bb48cf3bfecd1160ea89a83e7145dc3306</t>
+          <t>bcb11035c03a9e4bf16984a96758fc274729dc145490e8297d055e3df4304eb7</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>15シート。4調査の集計と限界・留保</t>
+          <t>見える化B系列の受領点検。認定者数・認定率の確認</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3060,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
@@ -3108,40 +3071,40 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>1f6b4f2c30ab5f154df5c839a5dea40c209a907eb6ddae1d7ad4228298875151</t>
+          <t>a13142fa18f80a6669f421b1e312b47d8b5fa0458d2c4e429323ce6ed8741a57</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>見える化B系列の受領点検。認定者数・認定率の確認</t>
+          <t>見える化D系列の受領点検。受給者数・利用率の確認</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>根拠</t>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>原データ</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_エビデンス_0_索引.xlsx</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>849d887263f44bbdf5afae53cfcc49c578484f12bf10c19da1f70d59c01a5ec6</t>
+          <t>7281003092774129ec979bd6a85de922a97c49b981965b3a52b3b34234ee3257</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>見える化D系列の受領点検。受給者数・利用率の確認</t>
+          <t>出典一覧12件と収録の範囲</t>
         </is>
       </c>
     </row>
@@ -3153,23 +3116,23 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_エビデンス_0_索引.xlsx</t>
+          <t>第10期計画_エビデンス_1_統計データ.xlsx</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>8</v>
+        <v>214</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>1e71b3073200cdb9b895285696ac997fc066be56ac577c3aef638fc737277fd8</t>
+          <t>46ac5f5fd1cde44cf0e840c8983cbca4f01814245ec605c76a6b6154544dfa42</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>出典一覧12件と収録の範囲</t>
+          <t>7シート。人口A系列・住民基本台帳・認定B系列・受給D系列・事業所K系列・従事者M系列・保険料C1</t>
         </is>
       </c>
     </row>
@@ -3181,23 +3144,23 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_エビデンス_1_統計データ.xlsx</t>
+          <t>第10期計画_エビデンス_2_事業所と公表情報.xlsx</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>214</v>
+        <v>42</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>adf625cf737e3234fa5124176a0cd90a0f2a5c3e19194445a7bc047076ba92c1</t>
+          <t>922db5b9a6eea453022b2393b902befd721b8c61d3215968afb90703a5e3141b</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>7シート。人口A系列・住民基本台帳・認定B系列・受給D系列・事業所K系列・従事者M系列・保険料C1</t>
+          <t>6シート。指定事業所124件・公表画面18件・施設名簿・実施地域</t>
         </is>
       </c>
     </row>
@@ -3209,86 +3172,58 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_エビデンス_2_事業所と公表情報.xlsx</t>
+          <t>第10期計画_エビデンス_3_調査の集計値.xlsx</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>70484137b2dcbcdb305810027db47943225201954d025d2cd4aaff4bb71fa96e</t>
+          <t>0fcf026abe6bd65b1844121cc2645630fe3925adf8f446a2b3012a86c50b616d</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>6シート。指定事業所124件・公表画面18件・施設名簿・実施地域</t>
+          <t>8シート。3調査の集計値・クロス集計・自由回答</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>原データ</t>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>参考</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_エビデンス_3_調査の集計値.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>57</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>8</v>
+        <v>48</v>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>13b60efa61888ed9312d4b76491ee2a0795e29f45d855d1f180fe6346dd49335</t>
+          <t>27442300bfcbacf909143f2d479492a23fac7167e872f3396efefffcf8a87a39</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>8シート。3調査の集計値・クロス集計・自由回答</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>372281afc8dff4da0f842bfda9e75b3c2ed9fd7e6fc84cc270020580622aaa7a</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
           <t>工程上の位置づけ（仕様書5の令和8年8月）</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="39" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="24" ht="39" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>注1）SHA-256は、ファイルの内容が同一であることを確認するための値である。受領したファイルのハッシュを算定し、本表の値と一致することを確認いただきたい。注2）本ファイル（根拠対照表）自身のハッシュは、本表を作成した後に確定するため記載していない。注3）シート数は Excel のシート数である。注4）検証用ZIPには、上記のほか図表の画像（PNG34点）を「03_図表」フォルダに収めている。計画素案及び中間報告に用いた図である。画像はハッシュを個別に記載していない。</t>
         </is>
@@ -3296,8 +3231,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3379,7 +3314,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>★中間報告の中心的な主張。「未達であるが実態が悪化したとは言えない」の根拠</t>
+          <t>中間報告の中心的な主張。「未達であるが実態が悪化したとは言えない」の根拠</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3368,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>第9期の最大の特徴。第10期の課題設定の根拠</t>
+          <t>第9期の構造評価の対象。第10期の課題設定の根拠</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3395,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>★構造評価の結論。判定「なし」5施策は実績が届いても評価できない</t>
+          <t>構造評価の結論。判定「なし」5施策は実績が届いても評価できない</t>
         </is>
       </c>
     </row>
@@ -3595,7 +3530,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>★中間報告の第5節。本報告の中心</t>
+          <t>中間報告の第5節に対応する</t>
         </is>
       </c>
     </row>
@@ -3607,29 +3542,29 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>自己点検（レッドチーム29件）の網羅性</t>
+          <t>評価方法の妥当性確認の内容</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>第9期評価のレッドチームレビュー 01〜08シート</t>
+          <t>中間報告 第6節</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>①指摘29件の区分（重大11・中14・軽微4）を確認する。②対応済み・未対応の別を確認する。③修正した誤読3点が実際に本文へ反映されているか確認する。</t>
+          <t>①確認した6論点について、対応と残る留保を確認する。②対応の内容が本文に反映されているか確認する。</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>評価そのものの確からしさ</t>
+          <t>評価方法そのものの妥当性</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>注1）1・4・9に★を付している。この3項目が中間報告の骨格である。注2）1と2は一見すると逆の結論にみえる。粗率（全要介護度・年齢調整なし）と調整済み率（要介護2以上・性年齢調整あり）の違いによるものであり、中間報告ではこの2つを併記している。この点をとくにご確認いただきたい。</t>
+          <t>注1）1・4・9にを付している。この3項目が中間報告の骨格である。注2）1と2は一見すると逆の結論にみえる。粗率（全要介護度・年齢調整なし）と調整済み率（要介護2以上・性年齢調整あり）の違いによるものであり、中間報告ではこの2つを併記している。この点をとくにご確認いただきたい。</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3714,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>★自給率（美瑛77.5％・東川67.1％・東神楽63.2％）の元数値を確認できない</t>
+          <t>自給率（美瑛77.5％・東川67.1％・東神楽63.2％）の元数値を確認できない</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3825,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>★「中」と「弱」の線引きが一貫しているか。個別の施策で判定を変えるべきものがないか</t>
+          <t>「中」と「弱」の線引きが一貫しているか。個別の施策で判定を変えるべきものがないか</t>
         </is>
       </c>
     </row>
@@ -3971,7 +3906,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>★この解釈が妥当か。年齢構成以外の要因を排除できているか</t>
+          <t>この解釈が妥当か。年齢構成以外の要因を排除できているか</t>
         </is>
       </c>
     </row>
@@ -3983,12 +3918,12 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>修正した誤読3点の選定</t>
+          <t>作成過程で記述を改めた3点の選定</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>レッドチーム29件のうち主要なものを3点挙げた。</t>
+          <t>自主点検で見直した記述のうち、本文への影響が大きいものを3点挙げた。</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -3998,7 +3933,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>3点以外に本文へ影響した修正がないか</t>
+          <t>3点以外に本文へ影響した見直しがないか</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -960,27 +960,27 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>要介護3以上認定率</t>
+          <t>重度要介護認定率（要介護3以上）　R7目標6.5％に対し実績6.3％</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>6.3％（令和8年3月末）</t>
+          <t>基準6.7％（R5）／R6 6.6％・R7 6.5％・R8 6.4％（目標）／6.3％（R8年3月末）</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>見える化B4-a</t>
+          <t>第9期介護保険事業計画（目標値）、見える化B4-a</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>エビデンス1 統計データ 03_認定_見える化B系列</t>
+          <t>妥当性検証報告書 02_第9期KPIの妥当性／エビデンス1 統計データ 03_認定_見える化B系列</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>B4-aの要介護3以上を確認する</t>
+          <t>第9期計画の年度目標値を確認し、B4-aの要介護3以上と比較する</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1108,27 +1108,27 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>通いの場への参加率</t>
+          <t>通いの場への参加率　R7目標9.0％に対し実績8.8％</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>8.0％（目標）→8.8％（令和7年）</t>
+          <t>基準7.3％（R4）／R6 8.0％・R7 9.0％・R8 10.0％（目標）／8.8％（R7）</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>2025年健康とくらしの調査【問5】1）</t>
+          <t>第9期介護保険事業計画（目標値）、2025年健康とくらしの調査【問5】1）</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析 11_KPIのデータ源の再検討</t>
+          <t>妥当性検証報告書 02_第9期KPIの妥当性／調査クロス集計・分析 11_KPIのデータ源の再検討</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>通いの場に月1回以上参加した者÷回答者</t>
+          <t>第9期計画の年度目標値を確認し、通いの場に月1回以上参加した者÷回答者と比較する</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>介護サービス自給率（6区分平均）</t>
+          <t>介護サービス自給率　算定可能区分の単純平均（美瑛6区分、東川・東神楽5区分）</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>6区分の単純平均。東川・東神楽は多機能系が算定できず5区分</t>
+          <t>算定できる区分の単純平均。東川・東神楽は多機能系が算定できず5区分のため、町間の順位付けや整備方針の直接の根拠には用いない</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>施策の空白5領域</t>
+          <t>調査に所見があるが対応する施策を確認できない5領域</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>主張の根拠水準の棚卸しと再レビュー 06_不足資料一覧</t>
+          <t>必要事項の一覧 01_資料の提供／確認依頼書</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>主張の根拠水準の棚卸しと再レビュー 06_不足資料一覧</t>
+          <t>必要事項の一覧 01_資料の提供／確認依頼書</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>計画素案の別管理表 03・04シート／レビュー指摘への対応と決定事項一覧 03シート</t>
+          <t>計画素案の別管理表 03・04シート／発注者確認事項一覧 01_委員会決定事項一覧</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -2654,7 +2654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>4b06eecdd9e32b179844e3b2745585d7045c503987d4b28500140e4fd78f7929</t>
+          <t>d3509f3472faefb8e9009ee6f95aeda655f05668f3e9cac3ce5c6aaced8304d6</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>8cf4888348dd22055c7fb41a5204a146cdfb6b971c4d4e959007d83176bf5721</t>
+          <t>d7123a0f36b71034a8ac5e7bce816a6af1292f953d599b2d993eedd859896341</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>0a93a013b0a4afae4999a69d216821d25f28cb822f5abdb32df80d6630760cd8</t>
+          <t>50c11d7f7b9622ca8802f5a0baf20358e9efa12ba76ae0d6c8a971923edb461f</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>e997c65a7218dc508cddda3773e36185a1d385f0efc4b26c1e5f8a4d67e55c4c</t>
+          <t>bacb245f4358d6ac75192de499f3c47d462cd4ce64a6b0ce43f37157be1da084</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -2864,23 +2864,23 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>aeeac320205f4e97239b1d7cc74b0fd7e22565f4b33d020459bb8ac9dfe0ffc4</t>
+          <t>2dc81b018702947ef0e9a95e6dc2b2976f9fd80dfc2b4d8a40473d621aa7054b</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>8シート。主張ごとの根拠水準、不足資料18件</t>
+          <t>5シート。第9期と第10期の基本目標・施策・KPIの対照</t>
         </is>
       </c>
     </row>
@@ -2892,23 +2892,23 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>184414df7bc556d2c4c815e6d9154ef9c390545a7f551c7804fb77c5fb439d06</t>
+          <t>16cf63bd6a488580dfd60f62e6357c771ffbc61d2b37708b44e3a75a1ca1f5b3</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>5シート。第9期と第10期の基本目標・施策・KPIの対照</t>
+          <t>認定率の年齢階級別・年齢調整の分析</t>
         </is>
       </c>
     </row>
@@ -2920,23 +2920,23 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>1c31def6332847387f7c2908ed866e58195a0e12e1aed56ba964734ab6314741</t>
+          <t>96042de30765ef578f6e0af3d13fc69889ab31cb1b4c3c6cce5dc7404f564526</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>認定率の年齢階級別・年齢調整の分析</t>
+          <t>自給率・給付水準の地域差の分析</t>
         </is>
       </c>
     </row>
@@ -2948,23 +2948,23 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>0d7b86ae9ff047a7db7df12dbaf2b44b9819f9522e3ba3e0e379f5a23c1d6b3d</t>
+          <t>e537a00c51947ea7319a71f0adb3c0fd4b0b49f9e72414ec246a0ca01bad00c9</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差の分析</t>
+          <t>24シート。健康とくらしの調査の個票によるクロス集計</t>
         </is>
       </c>
     </row>
@@ -2976,23 +2976,23 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>c407617d337c4dedfda93a26e65ec717d54647c58212f82e5806bf4450e0ef26</t>
+          <t>26d49174d41b77df79b2391cf29a929430c656194bf31d91b80fdb27853c5b6c</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>24シート。健康とくらしの調査の個票によるクロス集計</t>
+          <t>15シート。4調査の集計と限界・留保</t>
         </is>
       </c>
     </row>
@@ -3004,23 +3004,23 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>71485c441972aac9fe3afbf49b929c86e458de6b40b57c98a868102502101777</t>
+          <t>acca8189a6bcbf6a67a07ee8158fcbaa6743f28eb77e7522189d7edbe619ac6b</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>15シート。4調査の集計と限界・留保</t>
+          <t>見える化B系列の受領点検。認定者数・認定率の確認</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
@@ -3043,40 +3043,40 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>bcb11035c03a9e4bf16984a96758fc274729dc145490e8297d055e3df4304eb7</t>
+          <t>68457be3e2ee46b0befd5ad3d9bae17b80d774d55582eba797947ba2b2f936b7</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>見える化B系列の受領点検。認定者数・認定率の確認</t>
+          <t>見える化D系列の受領点検。受給者数・利用率の確認</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>根拠</t>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>原データ</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_エビデンス_0_索引.xlsx</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>a13142fa18f80a6669f421b1e312b47d8b5fa0458d2c4e429323ce6ed8741a57</t>
+          <t>770519d338c74e41b78fc4e0ef0d535e51129e136054b47c4d97357ca9341be6</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>見える化D系列の受領点検。受給者数・利用率の確認</t>
+          <t>出典一覧12件と収録の範囲</t>
         </is>
       </c>
     </row>
@@ -3088,23 +3088,23 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_エビデンス_0_索引.xlsx</t>
+          <t>第10期計画_エビデンス_1_統計データ.xlsx</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>8</v>
+        <v>214</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>7281003092774129ec979bd6a85de922a97c49b981965b3a52b3b34234ee3257</t>
+          <t>a6c35a07c5ca5620760078210bdcdce86d5f3f40c801e3dca5c0c7e0ba3b4834</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>出典一覧12件と収録の範囲</t>
+          <t>7シート。人口A系列・住民基本台帳・認定B系列・受給D系列・事業所K系列・従事者M系列・保険料C1</t>
         </is>
       </c>
     </row>
@@ -3116,23 +3116,23 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_エビデンス_1_統計データ.xlsx</t>
+          <t>第10期計画_エビデンス_2_事業所と公表情報.xlsx</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>214</v>
+        <v>42</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>46ac5f5fd1cde44cf0e840c8983cbca4f01814245ec605c76a6b6154544dfa42</t>
+          <t>15a8d9b68b872f9ed5ce5e3bdf9712fa280b0287ab1a9e2f6f9c1f27d2a9aa68</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>7シート。人口A系列・住民基本台帳・認定B系列・受給D系列・事業所K系列・従事者M系列・保険料C1</t>
+          <t>6シート。指定事業所124件・公表画面18件・施設名簿・実施地域</t>
         </is>
       </c>
     </row>
@@ -3144,86 +3144,58 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_エビデンス_2_事業所と公表情報.xlsx</t>
+          <t>第10期計画_エビデンス_3_調査の集計値.xlsx</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>922db5b9a6eea453022b2393b902befd721b8c61d3215968afb90703a5e3141b</t>
+          <t>1135b6daa1602d5988131d5af009a994d46b4ff981719c6f24601590db7c9caf</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>6シート。指定事業所124件・公表画面18件・施設名簿・実施地域</t>
+          <t>8シート。3調査の集計値・クロス集計・自由回答</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>原データ</t>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>参考</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_エビデンス_3_調査の集計値.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>57</v>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>8</v>
+        <v>49</v>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>0fcf026abe6bd65b1844121cc2645630fe3925adf8f446a2b3012a86c50b616d</t>
+          <t>f2bb23b1577097ecdd5cb749d9940f44d3112ba04260c02987853a49be4a7568</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>8シート。3調査の集計値・クロス集計・自由回答</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>27442300bfcbacf909143f2d479492a23fac7167e872f3396efefffcf8a87a39</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
           <t>工程上の位置づけ（仕様書5の令和8年8月）</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="39" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="23" ht="39" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>注1）SHA-256は、ファイルの内容が同一であることを確認するための値である。受領したファイルのハッシュを算定し、本表の値と一致することを確認いただきたい。注2）本ファイル（根拠対照表）自身のハッシュは、本表を作成した後に確定するため記載していない。注3）シート数は Excel のシート数である。注4）検証用ZIPには、上記のほか図表の画像（PNG34点）を「03_図表」フォルダに収めている。計画素案及び中間報告に用いた図である。画像はハッシュを個別に記載していない。</t>
         </is>
@@ -3231,8 +3203,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A23:F23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3407,7 +3379,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>施策の空白5領域の特定</t>
+          <t>調査に所見があるが対応する施策を確認できない5領域の特定</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3520,7 +3492,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>主張の根拠水準の棚卸しと再レビュー 06_不足資料一覧／第9期施策別評価表と暫定評価ルール 03シート</t>
+          <t>必要事項の一覧 01_資料の提供／第9期施策別評価表と暫定評価ルール 03シート</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -3837,7 +3809,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>施策の空白5領域の切り出し</t>
+          <t>調査に所見があるが対応する施策を確認できない5領域の切り出し</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>未利用認定者への働きかけが全国平均の39.2％</t>
+          <t>交付金評価「アウトリーチ等の取組状況」の得点が全国平均比39.2％（介護サービス利用率とは別の指標）</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>d3509f3472faefb8e9009ee6f95aeda655f05668f3e9cac3ce5c6aaced8304d6</t>
+          <t>4912bfb97aba1a83a3472fbdc4730d01339950ee1e0a5035685bd004883c444e</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>d7123a0f36b71034a8ac5e7bce816a6af1292f953d599b2d993eedd859896341</t>
+          <t>faed8c79d9fd58e75e397236b0517f3cac16d7f2dfe6e8cb446e7ad5855cf617</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>50c11d7f7b9622ca8802f5a0baf20358e9efa12ba76ae0d6c8a971923edb461f</t>
+          <t>55a61808b68bd9eae451913d888acb0884ffbeacb2dc2478176764a966e691b6</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>bacb245f4358d6ac75192de499f3c47d462cd4ce64a6b0ce43f37157be1da084</t>
+          <t>974a778706214e5915c1720dfedd1169a2e1424b5d929697b5b629cc0ed3fe5c</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>2dc81b018702947ef0e9a95e6dc2b2976f9fd80dfc2b4d8a40473d621aa7054b</t>
+          <t>1ed5c54ba0603bf316b85980033533e448a062fb0f1f8a7ae302d4ab4f3f7bc5</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>16cf63bd6a488580dfd60f62e6357c771ffbc61d2b37708b44e3a75a1ca1f5b3</t>
+          <t>61e68b6585f798f412ef63a749772ca35a4d847347a52ac2ec06c84c65980542</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>96042de30765ef578f6e0af3d13fc69889ab31cb1b4c3c6cce5dc7404f564526</t>
+          <t>c371615c44a8f151d1153ccb8d96b5360bbc281e2da23f2a1a0c6e6a0e09019d</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>e537a00c51947ea7319a71f0adb3c0fd4b0b49f9e72414ec246a0ca01bad00c9</t>
+          <t>85bc440e463f9de2ca636e69cfa40d4e818471911b9adf1d534fa33b837020d2</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>26d49174d41b77df79b2391cf29a929430c656194bf31d91b80fdb27853c5b6c</t>
+          <t>b18ee196eee5bbb11b9e98d2f91b7f41ba12e054c52af4f5f1d84e53d876f295</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>acca8189a6bcbf6a67a07ee8158fcbaa6743f28eb77e7522189d7edbe619ac6b</t>
+          <t>adf27245370b8e03f9e969b7b3ebe0086e41cdbaa9d5513d1240a7508eadf633</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>68457be3e2ee46b0befd5ad3d9bae17b80d774d55582eba797947ba2b2f936b7</t>
+          <t>6f43faf66d08b2df7cacf80caaf0b742de33b53a16a24a8c47970c321b03d189</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>770519d338c74e41b78fc4e0ef0d535e51129e136054b47c4d97357ca9341be6</t>
+          <t>605ff4b2f6f09e5f1633ac07c8152a8bd284cc9571ba56f7c31bfbf1231d5d5b</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>a6c35a07c5ca5620760078210bdcdce86d5f3f40c801e3dca5c0c7e0ba3b4834</t>
+          <t>aae6384d266ac1fd12d72f9d307c4de15c6701740ff773b52b82e9c6bfe1b8ff</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>15a8d9b68b872f9ed5ce5e3bdf9712fa280b0287ab1a9e2f6f9c1f27d2a9aa68</t>
+          <t>003e5e9ab0247342401d9742711bcc467835d6add87ae907e86c73d49b0e7471</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>1135b6daa1602d5988131d5af009a994d46b4ff981719c6f24601590db7c9caf</t>
+          <t>eabd34c9edcdd047cc7b0c306751f6038e77a0f2b8c5e4509a7d0969458bd98b</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>f2bb23b1577097ecdd5cb749d9940f44d3112ba04260c02987853a49be4a7568</t>
+          <t>55c83ffaa2a191514aa84c8d2ba98a6ca8679e0fd0bd2c43a29151a4d41988ed</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2724,7 +2724,7 @@
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>4912bfb97aba1a83a3472fbdc4730d01339950ee1e0a5035685bd004883c444e</t>
+          <t>6f960b34d39efaaf124f02b20ebd0055941c4f78ca5091c84b58d9e18d9d38c0</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>検証の対象。7節11表</t>
+          <t>検証の対象。7節12表</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>faed8c79d9fd58e75e397236b0517f3cac16d7f2dfe6e8cb446e7ad5855cf617</t>
+          <t>7afad22f4832a191380da0f8e9b73d0ad2c84ff0764028a8d3a6a18fb459faa4</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>55a61808b68bd9eae451913d888acb0884ffbeacb2dc2478176764a966e691b6</t>
+          <t>4e89e89d90460f743304990d870905ffe6e46254f17e0241e49f03a28ef4eb62</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>974a778706214e5915c1720dfedd1169a2e1424b5d929697b5b629cc0ed3fe5c</t>
+          <t>4cf2e53b983c7647870d373b1da7f6f2d8ae77f7dcd453eef73e8c60321798c6</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>1ed5c54ba0603bf316b85980033533e448a062fb0f1f8a7ae302d4ab4f3f7bc5</t>
+          <t>483f863cf6b10a8ef12f505fd957417d513fdf9e15e0ba974c62cec670603b12</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>61e68b6585f798f412ef63a749772ca35a4d847347a52ac2ec06c84c65980542</t>
+          <t>7b7dfe05caf731dd8c21bebfb550282dae7a6facebe7c7165ea1f77c1c66c396</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>c371615c44a8f151d1153ccb8d96b5360bbc281e2da23f2a1a0c6e6a0e09019d</t>
+          <t>c04c2d9ac919ff265366a0146093007795551e846f7c0f7237a8510e6a938572</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>85bc440e463f9de2ca636e69cfa40d4e818471911b9adf1d534fa33b837020d2</t>
+          <t>bbd0ca37a2b5e42e57467f7e8ff22a02f7819fab60177a5063722266dea8a51a</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>b18ee196eee5bbb11b9e98d2f91b7f41ba12e054c52af4f5f1d84e53d876f295</t>
+          <t>fbd00377762d3a651c254a49bb8306b1adae69b7b56c96be788f403a6eeed9ee</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>adf27245370b8e03f9e969b7b3ebe0086e41cdbaa9d5513d1240a7508eadf633</t>
+          <t>3b65f49233de81de3c9dc827c98821b7618ccec1352f8aa7eb4e5f7404688791</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>6f43faf66d08b2df7cacf80caaf0b742de33b53a16a24a8c47970c321b03d189</t>
+          <t>0ef8ddc0e762012b5a6a66b293cd51520ecb4591872dbc6492253d689769bcc1</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>605ff4b2f6f09e5f1633ac07c8152a8bd284cc9571ba56f7c31bfbf1231d5d5b</t>
+          <t>d2aa5b6b92b1b1c5283da84f8944b39611e7f2b9fe0122ece198557877ccac38</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>aae6384d266ac1fd12d72f9d307c4de15c6701740ff773b52b82e9c6bfe1b8ff</t>
+          <t>78bd939589e5a1eabfc6d47322be70e00ce14a18c2a386adefbdde683fc6e476</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>003e5e9ab0247342401d9742711bcc467835d6add87ae907e86c73d49b0e7471</t>
+          <t>37362c282b58050a22f4c3ffde1e46af735eb94db7ddec1972d96629da6c2e9e</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>eabd34c9edcdd047cc7b0c306751f6038e77a0f2b8c5e4509a7d0969458bd98b</t>
+          <t>d58bb74f3bb708c5362f63e2ea494845570e4452397bb9b99fce9105dd30dd4c</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>55c83ffaa2a191514aa84c8d2ba98a6ca8679e0fd0bd2c43a29151a4d41988ed</t>
+          <t>f31a6f5817faa5ce53af0106134d363a946587da1119b75ae40de886092bd224</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>①不足資料18件のうち第9期の評価に関わる7件を確認する。②暫定評価ルールの5類型を確認する。</t>
+          <t>①不足資料16件のうち第9期の評価に関わる8件を確認する。②暫定評価ルールの5類型を確認する。</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2724,7 +2724,7 @@
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>6f960b34d39efaaf124f02b20ebd0055941c4f78ca5091c84b58d9e18d9d38c0</t>
+          <t>0930de426847fa39f6c53205ce42beab744964865a3f6e1e35bec0cdac5214a3</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>検証の対象。7節12表</t>
+          <t>検証の対象。7節13表</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>7afad22f4832a191380da0f8e9b73d0ad2c84ff0764028a8d3a6a18fb459faa4</t>
+          <t>a7d141d19f80669a322de8e53a44d659c8a6d5d4e7b2cc02b9b5b8c4b8251cfa</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>4e89e89d90460f743304990d870905ffe6e46254f17e0241e49f03a28ef4eb62</t>
+          <t>29a4d65f5a87583eb46e0502fd12660c42563ac956963b709c06cda3e8c07290</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>4cf2e53b983c7647870d373b1da7f6f2d8ae77f7dcd453eef73e8c60321798c6</t>
+          <t>7b6332965e89e69834cd6793ba598a97f6a9f40f99576455dd76ff3a5601e6d7</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>483f863cf6b10a8ef12f505fd957417d513fdf9e15e0ba974c62cec670603b12</t>
+          <t>80fb86b2344fb268bfd29ee55a6e0a37f9a2766623eaa47f0ca3f0c4e108da62</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>7b7dfe05caf731dd8c21bebfb550282dae7a6facebe7c7165ea1f77c1c66c396</t>
+          <t>d88dbb74a65b7e746ef6d3c681b0f79229810f9a9e0a6728644cc27e312f82fe</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>c04c2d9ac919ff265366a0146093007795551e846f7c0f7237a8510e6a938572</t>
+          <t>3f97f37077634d9264a61d323eb9740be308b87cc9beadbc88a639f280facfa8</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>bbd0ca37a2b5e42e57467f7e8ff22a02f7819fab60177a5063722266dea8a51a</t>
+          <t>9322c3d304c5e536edd2c888845ce0c203847891b190931dec23cc873182386a</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>fbd00377762d3a651c254a49bb8306b1adae69b7b56c96be788f403a6eeed9ee</t>
+          <t>a76905857e4bd8fb171ffa99da23601e4d6f7328324315db79233e3fadfb1a3e</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>3b65f49233de81de3c9dc827c98821b7618ccec1352f8aa7eb4e5f7404688791</t>
+          <t>ef7b61a04d373a9d38909d57ba9c6bfcd4d90dc56baa27f752d67af91b12164b</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>0ef8ddc0e762012b5a6a66b293cd51520ecb4591872dbc6492253d689769bcc1</t>
+          <t>3c63cdfd146ecdf47f97f3f4a8112579240b8ff7f3a447aa272841ece3fa1fcb</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>f31a6f5817faa5ce53af0106134d363a946587da1119b75ae40de886092bd224</t>
+          <t>b2030bc243ad2d96670adb556a5ee739bc936424485d81c06df4f32fb3d15f7f</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>①不足資料16件のうち第9期の評価に関わる8件を確認する。②暫定評価ルールの5類型を確認する。</t>
+          <t>①不足資料17件のうち第9期の評価に関わる8件を確認する。②暫定評価ルールの5類型を確認する。</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2733,7 +2733,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>0930de426847fa39f6c53205ce42beab744964865a3f6e1e35bec0cdac5214a3</t>
+          <t>b8a4f574a12d69389c1db9dd6783add18641eb9393dd9dc532792c1196a2deae</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>29a4d65f5a87583eb46e0502fd12660c42563ac956963b709c06cda3e8c07290</t>
+          <t>3016a678280003a58aefd9796bbd22585cf4a11a7624b1d6901695e6f779c008</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>7b6332965e89e69834cd6793ba598a97f6a9f40f99576455dd76ff3a5601e6d7</t>
+          <t>9a9c0919691bdb2b1fdf8452995495377e24364cc58bac552c910f6da7eb22df</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>3c63cdfd146ecdf47f97f3f4a8112579240b8ff7f3a447aa272841ece3fa1fcb</t>
+          <t>fd43846f81979cbdb628a5d579d20cfe3f863b56ddb4bd3201a055667e0ba861</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>b2030bc243ad2d96670adb556a5ee739bc936424485d81c06df4f32fb3d15f7f</t>
+          <t>439cee401942e5520db18b5bb2761c0c2831dddbed22f5c4f758934b2388be3b</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2733,7 +2733,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>b8a4f574a12d69389c1db9dd6783add18641eb9393dd9dc532792c1196a2deae</t>
+          <t>de6db1b5a945da3cc7be25108360107cdc8a89e432e88cf5198fbaded63e5f45</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>a7d141d19f80669a322de8e53a44d659c8a6d5d4e7b2cc02b9b5b8c4b8251cfa</t>
+          <t>aa895678409a6e4ed3a0d50e8b300a23c893548c0163725d8d57e885b915bece</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>3016a678280003a58aefd9796bbd22585cf4a11a7624b1d6901695e6f779c008</t>
+          <t>b08309dfc3b31d28a148b852fdc7fe27c4a089dc19233117275b6587b7066a18</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>9a9c0919691bdb2b1fdf8452995495377e24364cc58bac552c910f6da7eb22df</t>
+          <t>7f0d6316866eeabcda9b3fe3a037f78e7aaafb211bde759ce7ef60f551af3d08</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>80fb86b2344fb268bfd29ee55a6e0a37f9a2766623eaa47f0ca3f0c4e108da62</t>
+          <t>d3e3dab585ee8695d3b4dadf3f6fa436bf2b6ec844b9e31c0092debb646b6014</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>3f97f37077634d9264a61d323eb9740be308b87cc9beadbc88a639f280facfa8</t>
+          <t>71246debdd975f630195b274e1839de145563055531755c0a0dc6b39d0b88fb3</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>a76905857e4bd8fb171ffa99da23601e4d6f7328324315db79233e3fadfb1a3e</t>
+          <t>28844d1682153e013daaddbf3359735b14a435e29463e635f84100c3dd892fa4</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>ef7b61a04d373a9d38909d57ba9c6bfcd4d90dc56baa27f752d67af91b12164b</t>
+          <t>3ac18f699fe546b8c6270b512e8d582d3e79b3a100bf9a339c25f77ec89896b8</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>fd43846f81979cbdb628a5d579d20cfe3f863b56ddb4bd3201a055667e0ba861</t>
+          <t>bab567f4c784e69bb5dcc5a7726dbaf169d34b521b6490f0f64a1552ce34bb3d</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>439cee401942e5520db18b5bb2761c0c2831dddbed22f5c4f758934b2388be3b</t>
+          <t>2bf24ff2fa273bc0f99baedc8e8cd4bb59684f607ecc4595a015f938bd3aea86</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2733,7 +2733,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>de6db1b5a945da3cc7be25108360107cdc8a89e432e88cf5198fbaded63e5f45</t>
+          <t>62337fabeac149bbc3b7ac41c4d2d3eeea56b716a157295177c750c2a8b0b5a3</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>aa895678409a6e4ed3a0d50e8b300a23c893548c0163725d8d57e885b915bece</t>
+          <t>8a90150605bbe806fd518db8853d5bc7844fcb332aad2ba86040b6e6c50353ae</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>b08309dfc3b31d28a148b852fdc7fe27c4a089dc19233117275b6587b7066a18</t>
+          <t>44e646e3292846aad1ff4c35b5d70e81c6ad838a7d3a222521fbdd8da1ff92a8</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>7f0d6316866eeabcda9b3fe3a037f78e7aaafb211bde759ce7ef60f551af3d08</t>
+          <t>b497a097fcda2972da18fcd97d858416fafd55a8abef8fe58e812dce146bd64a</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>d3e3dab585ee8695d3b4dadf3f6fa436bf2b6ec844b9e31c0092debb646b6014</t>
+          <t>1ae9ee7e70244291921f51499d7d0164a6a7b1d9f42a985baa6b30e7d13b3c2a</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>71246debdd975f630195b274e1839de145563055531755c0a0dc6b39d0b88fb3</t>
+          <t>b95707817ba0128048b7c2b2f164ca4f02133bbde6b2a5f1054dd2dca99a5dee</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>28844d1682153e013daaddbf3359735b14a435e29463e635f84100c3dd892fa4</t>
+          <t>308775e121a6dee6cf4383802da533fd71bf1a1856d1e6119b1b117a70a21d48</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>3ac18f699fe546b8c6270b512e8d582d3e79b3a100bf9a339c25f77ec89896b8</t>
+          <t>1f9de04a3d803eb37695f86f83fa2b60d0d8604f177e3d86b42d3f012e3e48d6</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>bab567f4c784e69bb5dcc5a7726dbaf169d34b521b6490f0f64a1552ce34bb3d</t>
+          <t>666a070077482f5e967d7718c3b19055a7c1c4a7f362f47dab7a55a86f10871c</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>2bf24ff2fa273bc0f99baedc8e8cd4bb59684f607ecc4595a015f938bd3aea86</t>
+          <t>7f5cc7a0e6a17a5d21a2cc692e8b43b434d9024c2ba4aa6d3ac4c04477d156ce</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>①不足資料17件のうち第9期の評価に関わる8件を確認する。②暫定評価ルールの5類型を確認する。</t>
+          <t>①不足資料18件のうち第9期の評価に関わる8件を確認する。②暫定評価ルールの5類型を確認する。</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2733,7 +2733,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>62337fabeac149bbc3b7ac41c4d2d3eeea56b716a157295177c750c2a8b0b5a3</t>
+          <t>12cc2686417b1b78f255ead42cfc0db7b48f093b36b74f28ccb22df538f34ece</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>8a90150605bbe806fd518db8853d5bc7844fcb332aad2ba86040b6e6c50353ae</t>
+          <t>d27a83b25ed4ce1acdfcbb5f0a911003f6e25fce960960bf37e2b64a6e6c189a</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>44e646e3292846aad1ff4c35b5d70e81c6ad838a7d3a222521fbdd8da1ff92a8</t>
+          <t>79d3ad52170ebe4242d4d52b4e9fd99e93b40d238b567179d788fb2b3b8b3606</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>b497a097fcda2972da18fcd97d858416fafd55a8abef8fe58e812dce146bd64a</t>
+          <t>9ce975635ee7ab4009f869142fc29750f8cbed33dd01c0e4de433946ef016b30</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>1ae9ee7e70244291921f51499d7d0164a6a7b1d9f42a985baa6b30e7d13b3c2a</t>
+          <t>9c72d5e2f2f942dbedf9e5c203918fc52322f398f0fb454fb7f07409c917ff55</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>b95707817ba0128048b7c2b2f164ca4f02133bbde6b2a5f1054dd2dca99a5dee</t>
+          <t>34004db0b4745642eddb5178729325f35700651241d86f68ead425ec63082f65</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>308775e121a6dee6cf4383802da533fd71bf1a1856d1e6119b1b117a70a21d48</t>
+          <t>2d00e20b546e9e4b9b80e4f8f93dc28f7b3c5666ddbe7f866eb744462f627cae</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>1f9de04a3d803eb37695f86f83fa2b60d0d8604f177e3d86b42d3f012e3e48d6</t>
+          <t>5f7aab4d5f6caa94a665f005b45af0adfa2ea5662a3b4cd197f63cb28115447d</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>666a070077482f5e967d7718c3b19055a7c1c4a7f362f47dab7a55a86f10871c</t>
+          <t>5ddc61f78a11879482f6dbd6d5d75129ba7a93288a6821514d4d61c2b633e2c3</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>7f5cc7a0e6a17a5d21a2cc692e8b43b434d9024c2ba4aa6d3ac4c04477d156ce</t>
+          <t>54b7443f108192a8763b24c6a8f72958a0bec8576e48784d5c23c16fc8323c64</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2733,7 +2733,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>12cc2686417b1b78f255ead42cfc0db7b48f093b36b74f28ccb22df538f34ece</t>
+          <t>2823f3c2f4a112442737ec42624058836ded4550a1c579e25ba0a624ce89f67c</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>d27a83b25ed4ce1acdfcbb5f0a911003f6e25fce960960bf37e2b64a6e6c189a</t>
+          <t>0387d8cc3723ebc0d0a0ac5e54a8d1ee94eb85be2081ff15514acf9b83b092a1</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>79d3ad52170ebe4242d4d52b4e9fd99e93b40d238b567179d788fb2b3b8b3606</t>
+          <t>bba1cba51cb9e8edc0d1ebdf47ab5a5d6ff5bb2643bf74a6558fec16259480da</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>9ce975635ee7ab4009f869142fc29750f8cbed33dd01c0e4de433946ef016b30</t>
+          <t>9beca9d0a294cf103ae566228ff9702547d13ec7f7fc6b66d9a3611faa16a96a</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>9c72d5e2f2f942dbedf9e5c203918fc52322f398f0fb454fb7f07409c917ff55</t>
+          <t>e6d7e0053ffd7938868a8e11598861a081b28e21a6efab4d6f9a455c1e3eafbd</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>34004db0b4745642eddb5178729325f35700651241d86f68ead425ec63082f65</t>
+          <t>e1d7639ba3e86154dd22e704fa3394c3f66a31da3096a4e93e51fb25dfa3bf9d</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>2d00e20b546e9e4b9b80e4f8f93dc28f7b3c5666ddbe7f866eb744462f627cae</t>
+          <t>e47d769a13555f5e761e567067b9e2cd24e24376a8d9fc4a3ddedaf42451b1b3</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>5f7aab4d5f6caa94a665f005b45af0adfa2ea5662a3b4cd197f63cb28115447d</t>
+          <t>b562ab03e12973fa2bbaaa61b58733299d813e38a723c7cc722eee444f8d3bf0</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>5ddc61f78a11879482f6dbd6d5d75129ba7a93288a6821514d4d61c2b633e2c3</t>
+          <t>c7febbb1c6a126886d81df9b5e93ed1f69e64cda5c979b7a9259a3688c4014ce</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>54b7443f108192a8763b24c6a8f72958a0bec8576e48784d5c23c16fc8323c64</t>
+          <t>a9dc402bd4fd1bda17523658b2515cca8df1aaff865f49464ba59376ce61462d</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2733,7 +2733,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>2823f3c2f4a112442737ec42624058836ded4550a1c579e25ba0a624ce89f67c</t>
+          <t>6dbce2ac7c2f76315696e817f5e243059e714028585e785b479550aecfc165a6</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>0387d8cc3723ebc0d0a0ac5e54a8d1ee94eb85be2081ff15514acf9b83b092a1</t>
+          <t>120d03ad47c2a78369daf485f34b5ee349f0a1fac3f10c1f605d103ace750e56</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>bba1cba51cb9e8edc0d1ebdf47ab5a5d6ff5bb2643bf74a6558fec16259480da</t>
+          <t>d4b3493131209601d4bbb46326efcfcd95dccd3cb2a5ec09f6c1f3a9012441f6</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>9beca9d0a294cf103ae566228ff9702547d13ec7f7fc6b66d9a3611faa16a96a</t>
+          <t>6ba7059be32d531f4a8c371d99c52502942dd7a9522ff9ebc6f0ce21074fcdf4</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>e6d7e0053ffd7938868a8e11598861a081b28e21a6efab4d6f9a455c1e3eafbd</t>
+          <t>fd20d0a016aa12b5c686f4a935d5cc498a9e6f182d11b11f6789e279c2ffa8d8</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>e1d7639ba3e86154dd22e704fa3394c3f66a31da3096a4e93e51fb25dfa3bf9d</t>
+          <t>e6ff8494207189ef5cf493ad712f4bb3d7dfc005ae633975ad73613f3155938e</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>e47d769a13555f5e761e567067b9e2cd24e24376a8d9fc4a3ddedaf42451b1b3</t>
+          <t>143754e4f6ef6a53d855913a5196783a6c78167c6b13271cadc3f4280482ca4d</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>b562ab03e12973fa2bbaaa61b58733299d813e38a723c7cc722eee444f8d3bf0</t>
+          <t>09b301fc0f874eba7828fedee96ed89030e5b84c522a7f8cd6134db2204f1482</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>c7febbb1c6a126886d81df9b5e93ed1f69e64cda5c979b7a9259a3688c4014ce</t>
+          <t>5bdfac7d119250fd7cf1b111fc449eaf1e5da6f8cafa0cd47013bdc6c3f903cd</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>a9dc402bd4fd1bda17523658b2515cca8df1aaff865f49464ba59376ce61462d</t>
+          <t>d5dd66dfd79880275118935190c828e7b186b34b674f9289c91c1287acbc1a09</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2733,7 +2733,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>6dbce2ac7c2f76315696e817f5e243059e714028585e785b479550aecfc165a6</t>
+          <t>f6d76239034bf23ca36db9f802c1355e7180a01097c3a83d79ede765ec16cf5e</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>120d03ad47c2a78369daf485f34b5ee349f0a1fac3f10c1f605d103ace750e56</t>
+          <t>aacdde24870aeb2d5b7ca3da063fbc21a7955327c5e6f5d31242f0f32452d57c</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>d4b3493131209601d4bbb46326efcfcd95dccd3cb2a5ec09f6c1f3a9012441f6</t>
+          <t>c48bedb15661059c4d05d08ff7863b1a20bf706bbd358a4aef43aa70568bf092</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>6ba7059be32d531f4a8c371d99c52502942dd7a9522ff9ebc6f0ce21074fcdf4</t>
+          <t>788f93276874fa1f7a700530ed221043ffe1a949e1306c6e328e3cb96247cd8d</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>fd20d0a016aa12b5c686f4a935d5cc498a9e6f182d11b11f6789e279c2ffa8d8</t>
+          <t>e0ad7e38909236f612f0968c5cdd6db4e7c2d82be271a97559faffabcf8f194c</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>e6ff8494207189ef5cf493ad712f4bb3d7dfc005ae633975ad73613f3155938e</t>
+          <t>0ce70ed466d7a22fa6d775f1a6b19848e4c4e042dd24fed6b2dcbf59e2eb81f6</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>143754e4f6ef6a53d855913a5196783a6c78167c6b13271cadc3f4280482ca4d</t>
+          <t>16b147c5e977e783c96a0d93ab4815b2a217143e2c8ff7e9e23cc60b9fb00b9b</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>09b301fc0f874eba7828fedee96ed89030e5b84c522a7f8cd6134db2204f1482</t>
+          <t>d3a3b381b89c7b3e77dc3d0e82a6e8935d721fa1bd015816e226bd10ffe76645</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>5bdfac7d119250fd7cf1b111fc449eaf1e5da6f8cafa0cd47013bdc6c3f903cd</t>
+          <t>9c6087b38e01d62a2dad8ef138e590eb020588653e9415fa5eb51b4cfc1da0da</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>d5dd66dfd79880275118935190c828e7b186b34b674f9289c91c1287acbc1a09</t>
+          <t>9bb84dc68a1ccd8fde3b83df7e37e51e4f66d6e7c0219df97f74cd9481041ce4</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2733,7 +2733,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>f6d76239034bf23ca36db9f802c1355e7180a01097c3a83d79ede765ec16cf5e</t>
+          <t>842756007dc63ac5b3051bb6901bc9b02a6cf3bdeb28a5afd4f9de7c29b9d80b</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>aacdde24870aeb2d5b7ca3da063fbc21a7955327c5e6f5d31242f0f32452d57c</t>
+          <t>171ea736d987459b56fb2330ae50f9878cd7ffafc94958ad1ebfbd067ab2006d</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>c48bedb15661059c4d05d08ff7863b1a20bf706bbd358a4aef43aa70568bf092</t>
+          <t>a1a28e426fb57a6d1b7b903160728484148a7de7e008c3412fbb00449f7a34a8</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>788f93276874fa1f7a700530ed221043ffe1a949e1306c6e328e3cb96247cd8d</t>
+          <t>f2667b0121c1e07c5d2b32d7a1aa64aac928ce0b6d880548d9b5d04a0d4e51f4</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>e0ad7e38909236f612f0968c5cdd6db4e7c2d82be271a97559faffabcf8f194c</t>
+          <t>f26e4646b5a01e25a9e3f560c52571871d9cd06ca59cdd4f24118aa71ff34ada</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>0ce70ed466d7a22fa6d775f1a6b19848e4c4e042dd24fed6b2dcbf59e2eb81f6</t>
+          <t>509bf89a3cfd9540bfc875134685e5652b32fe1009cac690936f7b3e55cac1ec</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>16b147c5e977e783c96a0d93ab4815b2a217143e2c8ff7e9e23cc60b9fb00b9b</t>
+          <t>934c8a4b507cc633188d2d6bd2762a3dcd424825aab6832df9282f8824999805</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>d3a3b381b89c7b3e77dc3d0e82a6e8935d721fa1bd015816e226bd10ffe76645</t>
+          <t>a3f875af1ad2eb078e4683ebb3222ce54582873b2fd747e1a74f1baffdcbd47d</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>9c6087b38e01d62a2dad8ef138e590eb020588653e9415fa5eb51b4cfc1da0da</t>
+          <t>f98023f442c01dc4b3b3e311e8e95f04f92fc0a871141985fb771d509a4752bd</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>9bb84dc68a1ccd8fde3b83df7e37e51e4f66d6e7c0219df97f74cd9481041ce4</t>
+          <t>048ca00359d2b841e306fef4f84ae70328dcb3a5bdc4c764fb719610d3becff1</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2733,7 +2733,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>842756007dc63ac5b3051bb6901bc9b02a6cf3bdeb28a5afd4f9de7c29b9d80b</t>
+          <t>e1d87633efec81c050e300935aa52523e7357eff319b4ecdc19c8eb5207e5051</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>171ea736d987459b56fb2330ae50f9878cd7ffafc94958ad1ebfbd067ab2006d</t>
+          <t>e7447a6fac7b25eb4bfead220345d3e629d79ce3aae05aeff126c9aaf1e4a63d</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>a1a28e426fb57a6d1b7b903160728484148a7de7e008c3412fbb00449f7a34a8</t>
+          <t>3c34313a708f2558ea2d9d67f98604bc38bc2a7f4fd640a9db82b80676da25ba</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>f2667b0121c1e07c5d2b32d7a1aa64aac928ce0b6d880548d9b5d04a0d4e51f4</t>
+          <t>0ee9c5c6c67361cdef711d9bed317f898dc99a04fc9282b7da62a6aef4001eb5</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>f26e4646b5a01e25a9e3f560c52571871d9cd06ca59cdd4f24118aa71ff34ada</t>
+          <t>fdff1c567a4c077b2b0d893c30bb4075db81f10a702a417722743740faf10a8f</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>509bf89a3cfd9540bfc875134685e5652b32fe1009cac690936f7b3e55cac1ec</t>
+          <t>936dbb7596e3a0ae23e6a5f7d669b0c5c8d4765ac8a35b49255791709fa5a73b</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>934c8a4b507cc633188d2d6bd2762a3dcd424825aab6832df9282f8824999805</t>
+          <t>529c1d0d69de96401247e1786b755382346d0ed47c2484613d2787944db3f0a0</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>a3f875af1ad2eb078e4683ebb3222ce54582873b2fd747e1a74f1baffdcbd47d</t>
+          <t>39dd96377ebb1fad2a64afd382de684842100184b7212ceee4f889128b50d5f0</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>f98023f442c01dc4b3b3e311e8e95f04f92fc0a871141985fb771d509a4752bd</t>
+          <t>56c093fef60a098d0fe64232c8b35493ecd98198cdc9de4f0d3879e6aec43ef6</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>048ca00359d2b841e306fef4f84ae70328dcb3a5bdc4c764fb719610d3becff1</t>
+          <t>6a48ca25ea9e5dbc90c4b4446cce77e650c2704e2375ba013da5035bcb22760b</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2733,7 +2733,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>e1d87633efec81c050e300935aa52523e7357eff319b4ecdc19c8eb5207e5051</t>
+          <t>d571055b13d843bce1b2fcb76df827a6c7e74c2733c62f766fcd602b4c527eb6</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>e7447a6fac7b25eb4bfead220345d3e629d79ce3aae05aeff126c9aaf1e4a63d</t>
+          <t>78a79d2f82e923fb8264cc5dadf3e6a56dbc849acb47242ab535370e3a58dac1</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>3c34313a708f2558ea2d9d67f98604bc38bc2a7f4fd640a9db82b80676da25ba</t>
+          <t>e12a69e84a4efc86d3a811e18b9879c44b7a8e02d94cb0808a406ecce2e7436b</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>0ee9c5c6c67361cdef711d9bed317f898dc99a04fc9282b7da62a6aef4001eb5</t>
+          <t>1b964299aa317c43b89c2caefd74a6271958c99d30924b3afbaa381b3b65a565</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>fdff1c567a4c077b2b0d893c30bb4075db81f10a702a417722743740faf10a8f</t>
+          <t>d401fc3e6341604a75fa4d624180d181a62fa46eb0bb6abe740b7bf424337a2f</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>936dbb7596e3a0ae23e6a5f7d669b0c5c8d4765ac8a35b49255791709fa5a73b</t>
+          <t>96dd3842ed2dd7fd09b49e8bda3aba79147ad28d7b92aa5585d2c797ca797f7a</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>529c1d0d69de96401247e1786b755382346d0ed47c2484613d2787944db3f0a0</t>
+          <t>d479dfaa597513d25328fc30db26b794b98346efacb52291ac59b1fad2d73df2</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>39dd96377ebb1fad2a64afd382de684842100184b7212ceee4f889128b50d5f0</t>
+          <t>275ec02440574394b292da4f70c8d1d91ae8fd1d52746854f4f468b1af654559</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>56c093fef60a098d0fe64232c8b35493ecd98198cdc9de4f0d3879e6aec43ef6</t>
+          <t>79f40534ea7306b05510c940bd14ce393d2a94d8543317a58533ec59f25236de</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>6a48ca25ea9e5dbc90c4b4446cce77e650c2704e2375ba013da5035bcb22760b</t>
+          <t>88b27faf2b9fe12b50f033c021cea90e0a9a0722df6812d69128821d8e642038</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -600,12 +600,12 @@
     <row r="6" ht="100" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>① 対照は38件である</t>
+          <t>① 対照は44件である</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>中間報告の第1節から第6節までに記載した主要な数値・主張を38件抽出し、それぞれについて「出典」「本集のどのファイル・どのシートで確認できるか」「どのように検算できるか」を示した（01シート）。中間報告に現れる数値表現は延べ107・ユニーク91であり、本集はそのうち評価の判断に関わるものを抽出している。</t>
+          <t>中間報告の第1節から第6節までに記載した主要な数値・主張を44件抽出し、それぞれについて「出典」「本集のどのファイル・どのシートで確認できるか」「どのように検算できるか」を示した（01シート）。中間報告に現れる数値表現は延べ107・ユニーク91であり、本集はそのうち評価の判断に関わるものを抽出している。</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>01シートの「確からしさ」欄で、出典から直接確認できるもの（確定）と、受託者の判断が入るもの・留保があるものを分けている。出典から直接確認できるもの（「確定」）29件、受託者の判断や出典側の留保を伴うもの9件である。</t>
+          <t>01シートの「確からしさ」欄で、出典から直接確認できるもの（確定）と、受託者の判断が入るもの・留保があるものを分けている。出典から直接確認できるもの（「確定」）33件、受託者の判断や出典側の留保を伴うもの11件である。</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>中間報告の記述と根拠の対照（38件）</t>
+          <t>中間報告の記述と根拠の対照（44件）</t>
         </is>
       </c>
     </row>
@@ -1145,32 +1145,32 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>総合事業ベースでは全国平均の31％</t>
+          <t>総合事業ベースの参加率は令和6年度3.53％</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>31％</t>
+          <t>3.53％</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>介護予防・日常生活支援総合事業の実施状況（令和2年度）</t>
+          <t>介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査（令和6年度・令和8年8月受領）</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>妥当性検証報告書 20_通いの場の統計の比較</t>
+          <t>総合事業実施状況調査の受領点検 01シート／妥当性検証報告書 20_通いの場の統計の比較</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>総合事業ベースの参加率と全国平均を比較する</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>令和3年度以降は見える化にデータ登録がなく令和2年度が最新</t>
+          <t>参加者実人数330人を令和6年（2024年）の65歳以上人口9,346人で除す</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>確定</t>
         </is>
       </c>
     </row>
@@ -1621,54 +1621,54 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節3</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>19施策の評価可能性</t>
+          <t>総給付費の対計画比　R6 96.3％・R7 97.8％</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>強5・中5・弱4・なし5</t>
+          <t>計画2,924,324千円→実績2,817,194千円／計画2,979,919千円→実績2,915,307千円</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>第9期計画の施策体系、実施済み4調査、第10期代表KPI16項目</t>
+          <t>地域包括ケア「見える化」システム 総括表（令和8年8月31日受領）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー 01〜03シート</t>
+          <t>見える化総括表の受領点検 01シート</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>施策ごとに調査の裏づけと代表KPIの有無を確認し、判定規則を適用する</t>
-        </is>
-      </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>確定（判定は受託者の基準による）</t>
+          <t>総括表の総給付費の行の計画値・実績値・対計画比を確認する。実績値は介護保険事業状況報告年報の給付費合計と1円まで一致する</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>確定</t>
         </is>
       </c>
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節3</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>調査の裏づけがある施策</t>
+          <t>代表KPI H15（給付費の計画乖離率）　R6▲3.66％・R7▲2.17％</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>13施策（68.4％）</t>
+          <t>▲107,129,545円／▲64,611,875円</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー</t>
+          <t>見える化総括表の受領点検 01シート</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>19施策のうち調査欄が「―」でないものを数える</t>
+          <t>（実績－計画）÷計画×100 を年度別に算定する。目標は±5％以内</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
@@ -1695,17 +1695,17 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節3</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>代表KPIが対応する施策</t>
+          <t>施設サービス給付費は計画を上回り、居住系は下回る</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>10施策（52.6％）</t>
+          <t>施設104.3％・100.8％／居住系83.8％・88.3％</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー</t>
+          <t>見える化総括表の受領点検 01シート</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>19施策のうちKPI欄が「―」でないものを数える</t>
+          <t>総括表の3区分の対計画比を確認する。3区分の実績値の合計は総給付費に一致する（差0円）</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
@@ -1732,111 +1732,111 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節3</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>調査に所見があるが対応する施策を確認できない5領域</t>
+          <t>定期巡回・随時対応型訪問介護看護は2期続けて実績が伴わない</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>5領域</t>
+          <t>第8期は3か年とも計画72人・実績0人／第9期はR6計画60人・実績0人、R7計画60人・実績7人</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>実施済み4調査の所見と第9期の施策体系の突合</t>
+          <t>地域包括ケア「見える化」システム 総括表詳細（利用者数）</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー 05シート</t>
+          <t>見える化総括表の受領点検 02シート</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>調査に所見があり施策がないものを特定する</t>
+          <t>総括表詳細（1）の当該サービスの行を第7期から第9期まで確認する</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>確定（領域の切り方は受託者の整理による）</t>
+          <t>確定（0人の理由は未確認）</t>
         </is>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節3</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>自力移動の手段がない</t>
+          <t>地域密着型通所介護の対計画比は2か年とも66％台</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>20.6％</t>
+          <t>66.5％／66.6％（給付費）、65.4％／60.4％（延べ利用者数）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>2025年健康とくらしの調査</t>
+          <t>地域包括ケア「見える化」システム 総括表詳細（利用者数）（給付費）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析 03_外出手段と移動制約</t>
+          <t>見える化総括表の受領点検 02シート</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>外出時の交通手段の設問から算定する</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>確定</t>
+          <t>通所介護・通所リハビリテーションの対計画比と並べて確認する</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>確定（要因は未分解）</t>
         </is>
       </c>
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節3</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>外出頻度が月1〜3回以下</t>
+          <t>第9期の保険料基準額　計画6,428円に対し実績6,069円</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>8.5％</t>
+          <t>対計画比94％（準備基金取崩後）</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>地域包括ケア「見える化」システム 管理指標グラフ（保険料基準額）</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析 04_外出の抑制と生活動作の困りごと</t>
+          <t>見える化総括表の受領点検 03シート</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>外出頻度の設問から算定する</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>確定</t>
+          <t>期単位の計画と実績の合計の行を確認する</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>留保（令和8年度の実績が未登録の状態の値）</t>
         </is>
       </c>
     </row>
@@ -1848,32 +1848,32 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>美瑛町の面積</t>
+          <t>19施策の評価可能性</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>676.78km²</t>
+          <t>強5・中5・弱4・なし5</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>全国都道府県市区町村別面積調（国土地理院）</t>
+          <t>第9期計画の施策体系、実施済み4調査、第10期代表KPI16項目</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>計画素案 第1章第7節</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー 01〜03シート</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>面積調の値を確認する</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="inlineStr">
-        <is>
-          <t>確定</t>
+          <t>施策ごとに調査の裏づけと代表KPIの有無を確認し、判定規則を適用する</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>確定（判定は受託者の基準による）</t>
         </is>
       </c>
     </row>
@@ -1885,27 +1885,27 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>世話をしてくれる人がいない</t>
+          <t>調査の裏づけがある施策</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>8.7％（独居では32.4％）</t>
+          <t>13施策（68.4％）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>2025年健康とくらしの調査【大雪－問4】1）</t>
+          <t>同上</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析 10_介護の担い手と介護の意向</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>「そのような人はいない」と回答した者÷回答者（n=4,599）</t>
+          <t>19施策のうち調査欄が「―」でないものを数える</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>話し相手がいない</t>
+          <t>代表KPIが対応する施策</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>3.1％（独居では8.2％）</t>
+          <t>10施策（52.6％）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析 06_世帯構成とリスク</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>19施策のうちKPI欄が「―」でないものを数える</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
@@ -1959,86 +1959,86 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>交付金評価「アウトリーチ等の取組状況」の得点が全国平均比39.2％（介護サービス利用率とは別の指標）</t>
+          <t>調査に所見があるが対応する施策を確認できない5領域</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>39.2％</t>
+          <t>5領域</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金の評価指標</t>
+          <t>実施済み4調査の所見と第9期の施策体系の突合</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>妥当性検証報告書 23_交付金評価の分析</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー 05シート</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>該当する評価項目の得点を全国平均で除する</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>確定</t>
+          <t>調査に所見があり施策がないものを特定する</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>確定（領域の切り方は受託者の整理による）</t>
         </is>
       </c>
     </row>
     <row r="38" ht="40" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>第5節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>不足資料（第9期の評価に関わるもの）</t>
+          <t>自力移動の手段がない</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>7件</t>
+          <t>20.6％</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>受託者の整理</t>
+          <t>2025年健康とくらしの調査</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>必要事項の一覧 01_資料の提供／確認依頼書</t>
+          <t>調査クロス集計・分析 03_外出手段と移動制約</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>18件のうち第9期の評価に関わるものを抽出したもの</t>
-        </is>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>確定（抽出は受託者の判断）</t>
+          <t>外出時の交通手段の設問から算定する</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>確定</t>
         </is>
       </c>
     </row>
     <row r="39" ht="40" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>第5節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>不足資料（全体）</t>
+          <t>外出頻度が月1〜3回以下</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>18件</t>
+          <t>8.5％</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>必要事項の一覧 01_資料の提供／確認依頼書</t>
+          <t>調査クロス集計・分析 04_外出の抑制と生活動作の困りごと</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>同シートの件数を数える</t>
+          <t>外出頻度の設問から算定する</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
@@ -2065,125 +2065,347 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>第5節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>確認事項（第9期の評価に関わるもの）</t>
+          <t>美瑛町の面積</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>5件</t>
+          <t>676.78km²</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>受託者の整理</t>
+          <t>全国都道府県市区町村別面積調（国土地理院）</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>計画素案の別管理表 03・04シート／発注者確認事項一覧 01_委員会決定事項一覧</t>
+          <t>計画素案 第1章第7節</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>確認事項56件のうち第9期の評価に関わるものを抽出したもの</t>
-        </is>
-      </c>
-      <c r="G40" s="9" t="inlineStr">
-        <is>
-          <t>確定（抽出は受託者の判断）</t>
+          <t>面積調の値を確認する</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>確定</t>
         </is>
       </c>
     </row>
     <row r="41" ht="40" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>評価方法の妥当性確認で扱った論点</t>
+          <t>世話をしてくれる人がいない</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>6件</t>
+          <t>8.7％（独居では32.4％）</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>受託者による内部点検</t>
+          <t>2025年健康とくらしの調査【大雪－問4】1）</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>本表01シート及び中間報告 第6節</t>
+          <t>調査クロス集計・分析 10_介護の担い手と介護の意向</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>中間報告 第6節の表に掲げた論点を数える</t>
-        </is>
-      </c>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>確定（論点の抽出は受託者の判断）</t>
+          <t>「そのような人はいない」と回答した者÷回答者（n=4,599）</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>確定</t>
         </is>
       </c>
     </row>
     <row r="42" ht="40" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
+          <t>第4節</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>話し相手がいない</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>3.1％（独居では8.2％）</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>調査クロス集計・分析 06_世帯構成とリスク</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>第4節</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>交付金評価「アウトリーチ等の取組状況」の得点が全国平均比39.2％（介護サービス利用率とは別の指標）</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>39.2％</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金の評価指標</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>妥当性検証報告書 23_交付金評価の分析</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>該当する評価項目の得点を全国平均で除する</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>第5節</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>不足資料（第9期の評価に関わるもの）</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>7件</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>受託者の整理</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>必要事項の一覧 01_資料の提供／確認依頼書</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>18件のうち第9期の評価に関わるものを抽出したもの</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>確定（抽出は受託者の判断）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>第5節</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>不足資料（全体）</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>18件</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>必要事項の一覧 01_資料の提供／確認依頼書</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>同シートの件数を数える</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>第5節</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>確認事項（第9期の評価に関わるもの）</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>5件</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>受託者の整理</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>計画素案の別管理表 03・04シート／発注者確認事項一覧 01_委員会決定事項一覧</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>確認事項56件のうち第9期の評価に関わるものを抽出したもの</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>確定（抽出は受託者の判断）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="40" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
           <t>第6節</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>評価方法の妥当性確認で扱った論点</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>6件</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>受託者による内部点検</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>本表01シート及び中間報告 第6節</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>中間報告 第6節の表に掲げた論点を数える</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>確定（論点の抽出は受託者の判断）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="40" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>第6節</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>受給率×受給者単価は給付月額指数に一致しない</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>上川管内21保険者のうち16保険者で0.03を超える差</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>見える化D49・地域差指数</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>地域差の分析／妥当性検証報告書 13_受給率の内訳と推移</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>21保険者について受給率×単価と給付月額指数の差を算定する</t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="G48" s="8" t="inlineStr">
         <is>
           <t>確定</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>注1）節別の件数は第1節 1件、第3節1 10件、第3節2 12件、第4節 10件、第5節 3件、第6節 2件である。注2）「確からしさ」が「確定」でないものは、受託者の判断による抽出・判定が入るか、出典側に留保があるものである。注3）を付した項目は、とくに留意を要する。</t>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>注1）節別の件数は第1節 1件、第3節1 10件、第3節2 12件、第3節3 6件、第4節 10件、第5節 3件、第6節 2件である。注2）「確からしさ」が「確定」でないものは、受託者の判断による抽出・判定が入るか、出典側に留保があるものである。注3）を付した項目は、とくに留意を要する。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A43:G43"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A49:G49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2654,7 +2876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2724,7 +2946,7 @@
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -2733,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>d571055b13d843bce1b2fcb76df827a6c7e74c2733c62f766fcd602b4c527eb6</t>
+          <t>9835840d077aa65379784ec80bddad374d35c9b416edcbda04182b6a6280fb9e</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -2791,7 +3013,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>78a79d2f82e923fb8264cc5dadf3e6a56dbc849acb47242ab535370e3a58dac1</t>
+          <t>7d6e7fafebe38f801cc4d4bda395d0758f9fca24009f6bebdc49ec662ad597dd</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -2819,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>e12a69e84a4efc86d3a811e18b9879c44b7a8e02d94cb0808a406ecce2e7436b</t>
+          <t>945a1f4d002236feaa491287bd2ec107954bbc0db54ad7b9a94b1b9cf148ffa5</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2840,14 +3062,14 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>6</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>1b964299aa317c43b89c2caefd74a6271958c99d30924b3afbaa381b3b65a565</t>
+          <t>a67e11695c611ac282e845c35f3e7d7570b67d4792bf23cc8be9f71201cbd949</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -2875,7 +3097,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>d401fc3e6341604a75fa4d624180d181a62fa46eb0bb6abe740b7bf424337a2f</t>
+          <t>c35168deb81aaa523ad4493037b2afa117e7b90115b977193d50d53826b4f207</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -2931,7 +3153,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>96dd3842ed2dd7fd09b49e8bda3aba79147ad28d7b92aa5585d2c797ca797f7a</t>
+          <t>48acd5741c3960e1326fa762a7077d0c0f170931f41ef332ebb60ee068a96169</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -2987,7 +3209,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>d479dfaa597513d25328fc30db26b794b98346efacb52291ac59b1fad2d73df2</t>
+          <t>c2b6443e2be5aeef45f58b162d4f9b9bcd4c082a13616141954eada2c9e08e0a</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3015,7 +3237,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>275ec02440574394b292da4f70c8d1d91ae8fd1d52746854f4f468b1af654559</t>
+          <t>9ab4cb60dade841e25e9e5c9ea86c6632fc91c947f96994cef8f99ede7fbcc4a</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -3053,149 +3275,261 @@
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>9a8887af17d9488c6c547a96ecb31f4abdaf0788ae1dd3aad062b81a4939ac40</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>7シート。第9期の対計画比・サービス別の乖離・保険料基準額</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>9a9fc5cc683636140c4212e0a572c78e003c570f92d618c737281ee9ca0d944f</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>5シート。通いの場・一般介護予防事業の令和6年度実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>35cb0d5a5364f865b72f29f57bb1b495098eb0889a7772172e1be1220471b157</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>介護保険事業状況報告の年報・月報の受領点検</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>997184a26c00875f992fed9bfbbcb020222f4f2300ce32ca70e33b1dea1f3ca7</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>介護保険特別会計の決算額・基金の推移・年報様式4との対照</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>原データ</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>第10期計画_エビデンス_0_索引.xlsx</t>
         </is>
       </c>
-      <c r="C17" s="10" t="n">
+      <c r="C21" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D21" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>d2aa5b6b92b1b1c5283da84f8944b39611e7f2b9fe0122ece198557877ccac38</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>出典一覧12件と収録の範囲</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>原データ</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>第10期計画_エビデンス_1_統計データ.xlsx</t>
         </is>
       </c>
-      <c r="C18" s="10" t="n">
+      <c r="C22" s="10" t="n">
         <v>214</v>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D22" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>78bd939589e5a1eabfc6d47322be70e00ce14a18c2a386adefbdde683fc6e476</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>7シート。人口A系列・住民基本台帳・認定B系列・受給D系列・事業所K系列・従事者M系列・保険料C1</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>原データ</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>第10期計画_エビデンス_2_事業所と公表情報.xlsx</t>
         </is>
       </c>
-      <c r="C19" s="10" t="n">
+      <c r="C23" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D23" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>37362c282b58050a22f4c3ffde1e46af735eb94db7ddec1972d96629da6c2e9e</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>6シート。指定事業所124件・公表画面18件・施設名簿・実施地域</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>原データ</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>第10期計画_エビデンス_3_調査の集計値.xlsx</t>
         </is>
       </c>
-      <c r="C20" s="10" t="n">
+      <c r="C24" s="10" t="n">
         <v>57</v>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D24" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>d58bb74f3bb708c5362f63e2ea494845570e4452397bb9b99fce9105dd30dd4c</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>8シート。3調査の集計値・クロス集計・自由回答</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
-      <c r="C21" s="10" t="n">
+      <c r="C25" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>88b27faf2b9fe12b50f033c021cea90e0a9a0722df6812d69128821d8e642038</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>a8c2f010be9519d5351a2a2fe65b528b3f8067e6c9554cd7705ad57988289648</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>工程上の位置づけ（仕様書5の令和8年8月）</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="39" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="27" ht="39" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>注1）SHA-256は、ファイルの内容が同一であることを確認するための値である。受領したファイルのハッシュを算定し、本表の値と一致することを確認いただきたい。注2）本ファイル（根拠対照表）自身のハッシュは、本表を作成した後に確定するため記載していない。注3）シート数は Excel のシート数である。注4）検証用ZIPには、上記のほか図表の画像（PNG34点）を「03_図表」フォルダに収めている。計画素案及び中間報告に用いた図である。画像はハッシュを個別に記載していない。</t>
         </is>
@@ -3204,7 +3538,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A27:F27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3443,7 +3777,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>①目標の根拠とした統計と実績の統計を確認する。②総合事業ベースでは全国平均の31％であることを確認する。</t>
+          <t>①目標の根拠とした統計と実績の統計を確認する。②総合事業ベースでは令和6年度3.53％であり、令和2年度1.6％から回復したが国の水準8％を大きく下回ることを確認する。</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>945a1f4d002236feaa491287bd2ec107954bbc0db54ad7b9a94b1b9cf148ffa5</t>
+          <t>812a562adb892b032cb3ae66d7f46e84a367faf30c9e36d48e449cb836d38f5b</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3062,19 +3062,19 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>a67e11695c611ac282e845c35f3e7d7570b67d4792bf23cc8be9f71201cbd949</t>
+          <t>08c2f499da62e1f837e2c962181c9fead1ea0fd9575cea4a3f72d9397b064ce7</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>6シート。評価表の受け皿・入力様式・暫定ルール・スコアカード</t>
+          <t>7シート。評価表の受け皿・入力様式・暫定ルール・成果評価・スコアカード・交付金による19施策の暫定評価</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>d88dbb74a65b7e746ef6d3c681b0f79229810f9a9e0a6728644cc27e312f82fe</t>
+          <t>3027cbe063f4249c6928e3ac15894041a9ca33799a450ecd605c71eeeaea0635</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>d2aa5b6b92b1b1c5283da84f8944b39611e7f2b9fe0122ece198557877ccac38</t>
+          <t>5a608a29c03e2ee6790514c1d78fe1f5423e9b3453f3130ca3e9cd26ba35b8ea</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3426,14 +3426,14 @@
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>7</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>78bd939589e5a1eabfc6d47322be70e00ce14a18c2a386adefbdde683fc6e476</t>
+          <t>c597a8d65d4723f85938e2fb2d582cc575625966c2c5fb4e9ea776d75031818a</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3454,14 +3454,14 @@
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>6</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>37362c282b58050a22f4c3ffde1e46af735eb94db7ddec1972d96629da6c2e9e</t>
+          <t>caed13490cbf631212a3c9b23d4ed22655385bdeee3890f8642a65923c0b714a</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3482,14 +3482,14 @@
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>8</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>d58bb74f3bb708c5362f63e2ea494845570e4452397bb9b99fce9105dd30dd4c</t>
+          <t>dec73084546c92ae9564149103e9aea40af80f416d8f21953285473f1a0d88b9</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>a8c2f010be9519d5351a2a2fe65b528b3f8067e6c9554cd7705ad57988289648</t>
+          <t>3bce1b054f4a979b797ac1d6ed25bd7ca061fd3f40012abda5d9d0abbe218bbd</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>9835840d077aa65379784ec80bddad374d35c9b416edcbda04182b6a6280fb9e</t>
+          <t>f139b8f12df7b05cab8d139086f37ce4f815e55d9664e47937dcbae18683a88e</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>812a562adb892b032cb3ae66d7f46e84a367faf30c9e36d48e449cb836d38f5b</t>
+          <t>570e73a2d6d9c419ae7b11182ae618d5180ff547e24eee84b98838e7145644e0</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>08c2f499da62e1f837e2c962181c9fead1ea0fd9575cea4a3f72d9397b064ce7</t>
+          <t>4c9082749581454f730872b7ba36e3105c93564bac701cfd397f6e03acb8e23e</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>3027cbe063f4249c6928e3ac15894041a9ca33799a450ecd605c71eeeaea0635</t>
+          <t>9001989ced27a5787eb072be62e3264567de7213c1fc8fa1f5957e84ebffe661</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>3bce1b054f4a979b797ac1d6ed25bd7ca061fd3f40012abda5d9d0abbe218bbd</t>
+          <t>f95a6691ff18bcb2ae7d801d765bcf1950cd0977e13f74d31984b5e6b3cc41f1</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>f139b8f12df7b05cab8d139086f37ce4f815e55d9664e47937dcbae18683a88e</t>
+          <t>70721a5ff8256637b6b5f57d365e114015f3725b53ca9ad18fffa69a39c91ec6</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>7d6e7fafebe38f801cc4d4bda395d0758f9fca24009f6bebdc49ec662ad597dd</t>
+          <t>c06acd04c8b53d561ca2a5800f4b22d1f7a2c9db267cdf07cfe158db3a0308ad</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>570e73a2d6d9c419ae7b11182ae618d5180ff547e24eee84b98838e7145644e0</t>
+          <t>4216771030f2c054403525691f7ae162dcfe628fa02eb8b47ea79d558542c7f5</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>4c9082749581454f730872b7ba36e3105c93564bac701cfd397f6e03acb8e23e</t>
+          <t>49ecab0683c89d7ea49c4e43c0cedefd320c4a7349e7d3d9c9dc5d7eab6add61</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>c35168deb81aaa523ad4493037b2afa117e7b90115b977193d50d53826b4f207</t>
+          <t>82e7538c95fbf72d95a922bb04b96838a65c864e04009be66d0cd1c270d8a49a</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>9001989ced27a5787eb072be62e3264567de7213c1fc8fa1f5957e84ebffe661</t>
+          <t>44d163a63139eac91a6de0752f3eb93f9748552363eae845cea577c1ad88416d</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>48acd5741c3960e1326fa762a7077d0c0f170931f41ef332ebb60ee068a96169</t>
+          <t>0f59da56446b1482e591ebd8b8b41c84f339d01de672db61029621f3b6d0959c</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>c2b6443e2be5aeef45f58b162d4f9b9bcd4c082a13616141954eada2c9e08e0a</t>
+          <t>6e08f463a03686bd2375a3675e9be5036fb70b49315b13607ca498af4c02a83c</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>9ab4cb60dade841e25e9e5c9ea86c6632fc91c947f96994cef8f99ede7fbcc4a</t>
+          <t>4060db2901d2dc7ef0f48dea23c1681d827643cb800c2ad5045361ba48e196a5</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>79f40534ea7306b05510c940bd14ce393d2a94d8543317a58533ec59f25236de</t>
+          <t>8cb8a5f993b247b21b2c35ead9845607dde9684b98625f6439d34c2ad8b260f7</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>9a8887af17d9488c6c547a96ecb31f4abdaf0788ae1dd3aad062b81a4939ac40</t>
+          <t>2f002d9f3a23d32e396b0abd164c4b5d4bb09f61157290576587569afbec90b3</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>9a9fc5cc683636140c4212e0a572c78e003c570f92d618c737281ee9ca0d944f</t>
+          <t>01330343c347c55db3f3248e45318eb73b3c906a595b89100a9778ac0ee3407f</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>35cb0d5a5364f865b72f29f57bb1b495098eb0889a7772172e1be1220471b157</t>
+          <t>f7cec3510ae62f3add2a32de0d6df23b3f6f670f3215ab80531f19d4eaa7affb</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>997184a26c00875f992fed9bfbbcb020222f4f2300ce32ca70e33b1dea1f3ca7</t>
+          <t>5165375a65a8dddbebe816eb759e2ac85e8c57c3d839cba90301a6fa099ad256</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>5a608a29c03e2ee6790514c1d78fe1f5423e9b3453f3130ca3e9cd26ba35b8ea</t>
+          <t>d44c9a412706d369f81aac91e8fe83959fd1826dec1e18038f14289404714eec</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>c597a8d65d4723f85938e2fb2d582cc575625966c2c5fb4e9ea776d75031818a</t>
+          <t>0704b8a4fe1e2971ad48c597b10bd127440dab6e45b7a65704ec72dec2f797c2</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>caed13490cbf631212a3c9b23d4ed22655385bdeee3890f8642a65923c0b714a</t>
+          <t>25be2bc34dd75fa12367641a74c1940640835b40b9b6704bde3ee3c68e569446</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>dec73084546c92ae9564149103e9aea40af80f416d8f21953285473f1a0d88b9</t>
+          <t>ab743223c96931171d38dd49bcd501fdff9d71c0f4a4452a17becc4f91214f73</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>f95a6691ff18bcb2ae7d801d765bcf1950cd0977e13f74d31984b5e6b3cc41f1</t>
+          <t>01d9bb7f97fdbf274b14fe93d1b0c59309af0f3065bf6b9aacad41780a31e0e7</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
